--- a/NPS.xlsx
+++ b/NPS.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R52478fbe006e442e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="Rc8465996866347fa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -219,6 +219,248 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>2026-09-11 07:45:12</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HOSPEDAGEM</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Aplicativo BEES</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SETE QUEDAS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CENTRO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111084430</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3149613</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-11 07:05:26</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUBDISTRIBUIDOR</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Relacionamento com o Vendedor ou com o time Comercial</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Fácil entrar em contato com o vendedor, Vendedor ajuda a resolver problemas, Vendedor com postura profissional, Vendedor explica novidades úteis de produtos e do app BEES, A quantidade de visitas do vendedor é boa, O dia/horário da visita do vendedor é apropriado</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NAVIRAI</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>VILA INDUSTRIAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110911432</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3148815</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>2026-09-10 13:12:05</x:t>
         </x:is>
       </x:c>

--- a/NPS.xlsx
+++ b/NPS.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R068ee62790b64786"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R257af4c246314c6a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -219,7 +219,7 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>2026-09-14 13:00:37</x:t>
+          <x:t>2026-09-15 13:59:27</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -263,23 +263,27 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Score 5</x:t>
+        </x:is>
+      </x:c>
       <x:c t="inlineStr">
         <x:is>
           <x:t>MS</x:t>
@@ -287,22 +291,22 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>CAARAPO</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>DISTRITO NOVA AMERICA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>110955288</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>3144547</x:t>
+          <x:t>NAVIRAI</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CENTRO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110974784</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3143309</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -312,7 +316,7 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>2026-09-14 12:30:18</x:t>
+          <x:t>2026-09-15 13:51:47</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -347,7 +351,7 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>MERCADO</x:t>
+          <x:t>BAR</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -372,11 +376,7 @@
       <x:c/>
       <x:c/>
       <x:c/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Vizinhança</x:t>
-        </x:is>
-      </x:c>
+      <x:c/>
       <x:c t="inlineStr">
         <x:is>
           <x:t>MS</x:t>
@@ -384,22 +384,22 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>NOVA ANDRADINA</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>NOVA CASA VERDE</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>111123228</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>3145450</x:t>
+          <x:t>ANTONIO JOAO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CENTRO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110980582</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3151325</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -409,7 +409,7 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>2026-09-14 11:41:50</x:t>
+          <x:t>2026-09-15 12:15:16</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -444,7 +444,7 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>BAR</x:t>
+          <x:t>MERCADO</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -453,23 +453,27 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vizinhança</x:t>
+        </x:is>
+      </x:c>
       <x:c t="inlineStr">
         <x:is>
           <x:t>MS</x:t>
@@ -477,22 +481,22 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>DOURADOS</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>SITIOCAS CAMPINA VERDE</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>111087959</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>3143102</x:t>
+          <x:t>RIO BRILHANTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CENTRO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111033365</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3149628</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -502,6 +506,442 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>2026-09-15 05:24:51</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>LC</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Eu realizo o meu pedido na quinta esperando que ele chegue na sexta,pois sou pequeno comerciante e não consigo ter um estoque grande. Porém nunca chega na data prevista e tem me prejudicado</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vizinhança</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>IVINHEMA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GUIRAI</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110953536</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3158454</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-14 13:00:37</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BAR</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CAARAPO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DISTRITO NOVA AMERICA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110955288</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3144547</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-14 12:30:18</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MERCADO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vizinhança</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NOVA ANDRADINA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NOVA CASA VERDE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111123228</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3145450</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-14 11:41:50</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BAR</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Programa Pontos, App Bees, Logística, Preços, Vendas, Financeiro, Materiais</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Preços são atrativos no BEES</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Entendo como receber materiais de apoio (cartaz, cervegela, etc.)</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vendedor ajuda a resolver problemas</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Fácil resolver problemas com produtos entregues danificados</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Formas de pagamento disponíveis são boas</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>O app BEES é rápido</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Os pontos são atribuídos ou reembolsados corretamente</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SITIOCAS CAMPINA VERDE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111087959</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3143102</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>2026-09-14 09:41:06</x:t>
         </x:is>
       </x:c>
@@ -548,19 +988,71 @@
       <x:c s="8">
         <x:v>3</x:v>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Logística</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Dias de entrega disponíveis não são bons, As entregas chegam com atraso</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
       <x:c/>
       <x:c/>
       <x:c t="inlineStr">

--- a/NPS.xlsx
+++ b/NPS.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R257af4c246314c6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R3f741201d4f54549"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -219,7 +219,7 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>2026-09-15 13:59:27</x:t>
+          <x:t>2026-09-16 21:46:52</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -254,36 +254,36 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>BAR</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>promotor</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Score 5</x:t>
-        </x:is>
-      </x:c>
+          <x:t>LANCHONETE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>neutro</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Quando deixar um produto disponível para pedido, cumpra com a entrega , porque a partir do momento que fazemos o pedido contamos com o produto na data . Entende-se que se o produto está ali disponível é porque tem estoque . E se a pessoa pede é porque ela precisa . Aí o pedido chega e o produto simplesmente foi cortado do pedido . Isso não faz sentido. Ainda mais se tratando de uma empresa tão grande e renomeada .</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
       <x:c t="inlineStr">
         <x:is>
           <x:t>MS</x:t>
@@ -291,7 +291,7 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>NAVIRAI</x:t>
+          <x:t>MARACAJU</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -301,12 +301,12 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>110974784</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>3143309</x:t>
+          <x:t>111090879</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3154636</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -316,7 +316,7 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>2026-09-15 13:51:47</x:t>
+          <x:t>2026-09-16 11:17:48</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -351,7 +351,7 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>BAR</x:t>
+          <x:t>LC</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -376,7 +376,11 @@
       <x:c/>
       <x:c/>
       <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vizinhança</x:t>
+        </x:is>
+      </x:c>
       <x:c t="inlineStr">
         <x:is>
           <x:t>MS</x:t>
@@ -384,7 +388,7 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>ANTONIO JOAO</x:t>
+          <x:t>AMAMBAI</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -394,12 +398,12 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>110980582</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>3151325</x:t>
+          <x:t>111075802</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3141882</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -409,7 +413,7 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>2026-09-15 12:15:16</x:t>
+          <x:t>2026-09-16 10:46:10</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -444,7 +448,7 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>MERCADO</x:t>
+          <x:t>MERCEARIA</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -469,11 +473,7 @@
       <x:c/>
       <x:c/>
       <x:c/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Vizinhança</x:t>
-        </x:is>
-      </x:c>
+      <x:c/>
       <x:c t="inlineStr">
         <x:is>
           <x:t>MS</x:t>
@@ -481,22 +481,22 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>RIO BRILHANTE</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>CENTRO</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>111033365</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>3149628</x:t>
+          <x:t>ELDORADO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SPARTACO ASTOLFI</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111134035</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3151281</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -506,6 +506,494 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>2026-09-16 08:03:54</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MERCADO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vizinhança</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JARDIM GUANABARA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110945990</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3158590</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-15 13:59:27</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BAR</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Score 5</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NAVIRAI</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CENTRO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110974784</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3143309</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-15 13:51:47</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BAR</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>App Bees, Vendas</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Fácil entrar em contato com o vendedor, Vendedor ajuda a resolver problemas, Vendedor com postura profissional, Vendedor explica novidades úteis de produtos e do app BEES, A quantidade de visitas do vendedor é boa, O dia/horário da visita do vendedor é apropriado</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>É Fácil encontrar a quantidade de produtos que preciso</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ANTONIO JOAO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CENTRO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110980582</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3151325</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-15 12:15:16</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MERCADO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vendas</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vendedor com postura profissional</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vizinhança</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RIO BRILHANTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CENTRO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111033365</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3149628</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>2026-09-15 05:24:51</x:t>
         </x:is>
       </x:c>
@@ -552,19 +1040,71 @@
       <x:c s="8">
         <x:v>10</x:v>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vendas</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vendedor ajuda a resolver problemas</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
       <x:c t="inlineStr">
         <x:is>
           <x:t>Eu realizo o meu pedido na quinta esperando que ele chegue na sexta,pois sou pequeno comerciante e não consigo ter um estoque grande. Porém nunca chega na data prevista e tem me prejudicado</x:t>

--- a/NPS.xlsx
+++ b/NPS.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R9f2a916d1ffb47e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R4bc9db7480814a82"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -219,7 +219,7 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>2026-09-21 17:14:55</x:t>
+          <x:t>2026-09-24 11:26:17</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -254,7 +254,7 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>RESTAURANTE</x:t>
+          <x:t>SUBDISTRIBUIDOR</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -265,19 +265,71 @@
       <x:c s="8">
         <x:v>10</x:v>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Preço, Vendas</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Fácil entrar em contato com o vendedor, Vendedor ajuda a resolver problemas, Vendedor explica novidades úteis de produtos e do app BEES, A quantidade de visitas do vendedor é boa</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
       <x:c/>
       <x:c/>
       <x:c t="inlineStr">
@@ -287,22 +339,22 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>AMAMBAI</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>CENTRO</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>110966120</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>3159617</x:t>
+          <x:t>DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ALTOS DO INDAIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110997980</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3149154</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -312,7 +364,7 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>2026-09-21 13:02:57</x:t>
+          <x:t>2026-09-24 10:30:05</x:t>
         </x:is>
       </x:c>
       <x:c t="inlineStr">
@@ -347,36 +399,84 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>MERCADO</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>promotor</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="8">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>Vizinhança</x:t>
-        </x:is>
-      </x:c>
+          <x:t>SUBDISTRIBUIDOR</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>detrator</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Preço, Preços</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>As promoções não valem a pena</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
       <x:c t="inlineStr">
         <x:is>
           <x:t>MS</x:t>
@@ -384,22 +484,22 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
-          <x:t>ANTONIO JOAO</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>CENTRO</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>110910450</x:t>
-        </x:is>
-      </x:c>
-      <x:c t="inlineStr">
-        <x:is>
-          <x:t>3141100</x:t>
+          <x:t>DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>PARQUE DAS NACOES</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111100911</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3144025</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -409,6 +509,1186 @@
       </x:c>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>2026-09-24 08:02:15</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUBDISTRIBUIDOR</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>App Bees, Logística, Financeiro</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>A equipe de entrega é profissional</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>O app BEES é rápido, BEES recomenda produtos relevantes, Fácil localizar produtos</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JARDIM GUAICURUS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110936612</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3150734</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-24 07:37:36</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MERCEARIA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vendas</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vendedor ajuda a resolver problemas, Vendedor com postura profissional</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>JARDIM NOVO HORIZONTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110997130</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3158257</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-24 05:30:21</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>NÃO DEFINIDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>detrator</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Preço</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Ter mais entregas !</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>PONTA PORA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>PARQUE DOS IPES I</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111043631</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3158611</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-23 07:09:26</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RESTAURANTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Preço</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>AMAMBAI</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CENTRO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111080796</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3159760</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-22 14:48:15</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>BAR</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Programa Pontos, App Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>É fácil atualizar ou cancelar pedidos</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>As ofertas de pontos valem a pena</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Clube Black, Score 5</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>VILA VARGAS/VILA SAP</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>111034590</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3155946</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-22 11:33:21</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MERCADO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Programa Pontos, App Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Notificações do app Bees são úteis</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>As ofertas de pontos são fáceis de entender</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Excelente</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vizinhança</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>VILA PLANALTO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110927873</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3142166</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-21 17:14:55</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>RESTAURANTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Preço</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>AMAMBAI</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CENTRO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110966120</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3159617</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>2026-09-21 13:02:57</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Bees</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>GRAN DOURADOS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>COM MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>SUPERCOM OESTE</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>REVENDA</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MERCADO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>promotor</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Programa Pontos, App Bees, Vendas</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Fácil entrar em contato com o vendedor, Vendedor ajuda a resolver problemas, Vendedor com postura profissional, Vendedor explica novidades úteis de produtos e do app BEES, A quantidade de visitas do vendedor é boa, O dia/horário da visita do vendedor é apropriado</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>É Fácil encontrar a quantidade de produtos que preciso</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>As ofertas de pontos valem a pena</x:t>
+        </x:is>
+      </x:c>
+      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Vizinhança</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MS</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>ANTONIO JOAO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>CENTRO</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>110910450</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>3141100</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="8">
+        <x:v>202609</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>2026-09-21 11:37:36</x:t>
         </x:is>
       </x:c>
@@ -455,19 +1735,71 @@
       <x:c s="8">
         <x:v>10</x:v>
       </x:c>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
-      <x:c/>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Preço</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
       <x:c/>
       <x:c/>
       <x:c t="inlineStr">
